--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIII/LTAIPT_A63F13.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIII/LTAIPT_A63F13.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47656CA-97AC-492C-86CC-9ADCD639C9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="228">
   <si>
     <t>48960</t>
   </si>
@@ -147,9 +153,6 @@
     <t>435921</t>
   </si>
   <si>
-    <t>435910</t>
-  </si>
-  <si>
     <t>435920</t>
   </si>
   <si>
@@ -228,23 +231,23 @@
     <t>Hipervínculo a la dirección electrónica del sistema</t>
   </si>
   <si>
-    <t>Nombre y cargos del personal habilitado en la Unidad de Transparencia 
+    <t>Persona responsable y personal habilitado para cumplir con las funciones de la Unidad de Transparencia (UT) 
 Tabla_435914</t>
   </si>
   <si>
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
-    <t>Fecha de validación</t>
-  </si>
-  <si>
     <t>Fecha de actualización</t>
   </si>
   <si>
     <t>Nota</t>
   </si>
   <si>
-    <t>2023</t>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>01/07/2024</t>
   </si>
   <si>
     <t>Carretera</t>
@@ -262,376 +265,424 @@
     <t>Ciudad</t>
   </si>
   <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>Tlaxcala</t>
   </si>
   <si>
     <t>33</t>
   </si>
   <si>
-    <t>29</t>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>246-46-2-08-12</t>
+  </si>
+  <si>
+    <t>08:30 a 17:30</t>
+  </si>
+  <si>
+    <t>transparencia@cobatlaxcala.edu.mx</t>
+  </si>
+  <si>
+    <t>Se reciben solicitudes de información pública respecto al Colegio de Bachileres del Estado de Tlaxcala, a través del correo electrónico oficial de la Unidad de Transparencia, en el domicilio oficial de ésta, vía telefónica, por correo postal, mensajería, telégrafo, verbalmente ante el personal habilitado que las capturará en el sistema electrónico de solicitudes; o cualquier medio aprobado por el Sistema Nacional</t>
+  </si>
+  <si>
+    <t>15984583</t>
+  </si>
+  <si>
+    <t>F99A931FA6631C9E56FB9265241B927D</t>
+  </si>
+  <si>
+    <t>01/04/2024</t>
+  </si>
+  <si>
+    <t>30/06/2024</t>
+  </si>
+  <si>
+    <t>http://www.infomextlaxcala.org.mx/</t>
+  </si>
+  <si>
+    <t>14416153</t>
+  </si>
+  <si>
+    <t>Unidad de Transparencia</t>
+  </si>
+  <si>
+    <t>Calle</t>
   </si>
   <si>
     <t>México</t>
   </si>
   <si>
-    <t>90000</t>
-  </si>
-  <si>
-    <t>246-46-2-08-12</t>
-  </si>
-  <si>
-    <t>119</t>
-  </si>
-  <si>
-    <t>08:30 a 17:30</t>
-  </si>
-  <si>
-    <t>transparencia@cobatlaxcala.edu.mx</t>
+    <t>Se reciben solicitudes de información pública respecto al Colegio de Bachileres del Estado de Tlaxcala, a través del correo electrónico oficial de la Unidad de Transparencia, en el domicilio oficial de ésta, vía telefónica, por correo postal, mensajería, telégrafo, verbalmente ante el personal habilitado que las capturará en el sistema electrónico de solicitudes; o cualquier medio aprobado por el Sistema Nacional de Transparencia</t>
+  </si>
+  <si>
+    <t>9958127</t>
+  </si>
+  <si>
+    <t>Privada</t>
+  </si>
+  <si>
+    <t>Eje vial</t>
+  </si>
+  <si>
+    <t>Circunvalación</t>
+  </si>
+  <si>
+    <t>Brecha</t>
+  </si>
+  <si>
+    <t>Diagonal</t>
+  </si>
+  <si>
+    <t>Corredor</t>
+  </si>
+  <si>
+    <t>Circuito</t>
+  </si>
+  <si>
+    <t>Pasaje</t>
+  </si>
+  <si>
+    <t>Vereda</t>
+  </si>
+  <si>
+    <t>Calzada</t>
+  </si>
+  <si>
+    <t>Viaducto</t>
+  </si>
+  <si>
+    <t>Prolongación</t>
+  </si>
+  <si>
+    <t>Boulevard</t>
+  </si>
+  <si>
+    <t>Peatonal</t>
+  </si>
+  <si>
+    <t>Retorno</t>
+  </si>
+  <si>
+    <t>Camino</t>
+  </si>
+  <si>
+    <t>Callejón</t>
+  </si>
+  <si>
+    <t>Cerrada</t>
+  </si>
+  <si>
+    <t>Ampliación</t>
+  </si>
+  <si>
+    <t>Continuación</t>
+  </si>
+  <si>
+    <t>Terracería</t>
+  </si>
+  <si>
+    <t>Andador</t>
+  </si>
+  <si>
+    <t>Periférico</t>
+  </si>
+  <si>
+    <t>Avenida</t>
+  </si>
+  <si>
+    <t>Aeropuerto</t>
+  </si>
+  <si>
+    <t>Barrio</t>
+  </si>
+  <si>
+    <t>Cantón</t>
+  </si>
+  <si>
+    <t>Ciudad industrial</t>
+  </si>
+  <si>
+    <t>Colonia</t>
+  </si>
+  <si>
+    <t>Condominio</t>
+  </si>
+  <si>
+    <t>Conjunto habitacional</t>
+  </si>
+  <si>
+    <t>Corredor industrial</t>
+  </si>
+  <si>
+    <t>Coto</t>
+  </si>
+  <si>
+    <t>Cuartel</t>
+  </si>
+  <si>
+    <t>Ejido</t>
+  </si>
+  <si>
+    <t>Exhacienda</t>
+  </si>
+  <si>
+    <t>Fracción</t>
+  </si>
+  <si>
+    <t>Fraccionamiento</t>
+  </si>
+  <si>
+    <t>Granja</t>
+  </si>
+  <si>
+    <t>Hacienda</t>
+  </si>
+  <si>
+    <t>Ingenio</t>
+  </si>
+  <si>
+    <t>Manzana</t>
+  </si>
+  <si>
+    <t>Paraje</t>
+  </si>
+  <si>
+    <t>Parque industrial</t>
+  </si>
+  <si>
+    <t>Pueblo</t>
+  </si>
+  <si>
+    <t>Puerto</t>
+  </si>
+  <si>
+    <t>Ranchería</t>
+  </si>
+  <si>
+    <t>Rancho</t>
+  </si>
+  <si>
+    <t>Región</t>
+  </si>
+  <si>
+    <t>Residencial</t>
+  </si>
+  <si>
+    <t>Rinconada</t>
+  </si>
+  <si>
+    <t>Sección</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Supermanzana</t>
+  </si>
+  <si>
+    <t>Unidad</t>
+  </si>
+  <si>
+    <t>Unidad habitacional</t>
+  </si>
+  <si>
+    <t>Villa</t>
+  </si>
+  <si>
+    <t>Zona federal</t>
+  </si>
+  <si>
+    <t>Zona industrial</t>
+  </si>
+  <si>
+    <t>Zona militar</t>
+  </si>
+  <si>
+    <t>Zona naval</t>
+  </si>
+  <si>
+    <t>Guerrero</t>
+  </si>
+  <si>
+    <t>Puebla</t>
+  </si>
+  <si>
+    <t>Quintana Roo</t>
+  </si>
+  <si>
+    <t>Guanajuato</t>
+  </si>
+  <si>
+    <t>Durango</t>
+  </si>
+  <si>
+    <t>Michoacán de Ocampo</t>
+  </si>
+  <si>
+    <t>San Luis Potosí</t>
+  </si>
+  <si>
+    <t>Campeche</t>
+  </si>
+  <si>
+    <t>Coahuila de Zaragoza</t>
+  </si>
+  <si>
+    <t>Nayarit</t>
+  </si>
+  <si>
+    <t>Zacatecas</t>
+  </si>
+  <si>
+    <t>Morelos</t>
+  </si>
+  <si>
+    <t>Sonora</t>
+  </si>
+  <si>
+    <t>Baja California Sur</t>
+  </si>
+  <si>
+    <t>Colima</t>
+  </si>
+  <si>
+    <t>Tabasco</t>
+  </si>
+  <si>
+    <t>Oaxaca</t>
+  </si>
+  <si>
+    <t>Jalisco</t>
+  </si>
+  <si>
+    <t>Chiapas</t>
+  </si>
+  <si>
+    <t>Hidalgo</t>
+  </si>
+  <si>
+    <t>Aguascalientes</t>
+  </si>
+  <si>
+    <t>Tamaulipas</t>
+  </si>
+  <si>
+    <t>Sinaloa</t>
+  </si>
+  <si>
+    <t>Yucatán</t>
+  </si>
+  <si>
+    <t>Chihuahua</t>
+  </si>
+  <si>
+    <t>Querétaro</t>
+  </si>
+  <si>
+    <t>Nuevo León</t>
+  </si>
+  <si>
+    <t>Veracruz de Ignacio de la Llave</t>
+  </si>
+  <si>
+    <t>Ciudad de México</t>
+  </si>
+  <si>
+    <t>Baja California</t>
+  </si>
+  <si>
+    <t>56316</t>
+  </si>
+  <si>
+    <t>56317</t>
+  </si>
+  <si>
+    <t>56318</t>
+  </si>
+  <si>
+    <t>77813</t>
+  </si>
+  <si>
+    <t>56319</t>
+  </si>
+  <si>
+    <t>81282</t>
+  </si>
+  <si>
+    <t>56320</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Nombre(s)</t>
+  </si>
+  <si>
+    <t>Primer apellido</t>
+  </si>
+  <si>
+    <t>Segundo apellido</t>
+  </si>
+  <si>
+    <t>Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>Denominación del cargo</t>
+  </si>
+  <si>
+    <t>Función en la UT</t>
+  </si>
+  <si>
+    <t>15F187DD5DCC75645596053986A796B9</t>
+  </si>
+  <si>
+    <t>Francisco Rene</t>
+  </si>
+  <si>
+    <t>Zempoalteca</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Capturista</t>
+  </si>
+  <si>
+    <t>Auxiliar administrativo</t>
   </si>
   <si>
     <t>Se reciben solicitudes de información pública respecto al Colegio de Bachileres del Estado de Tlaxcala, a través del correo electrónico oficial de la Unidad de Transparencia, en el domicilio oficial de ésta, vía telefónica, por correo postal, mensajería, telégrafo, verbalmente ante el personal habilitado que las capturará en el sistema electrónico de solicitudes; o cualquier medio aprobado por el Sistema Nacional de Transparencia.</t>
   </si>
   <si>
-    <t>https://www.plataformadetransparencia.org.mx</t>
-  </si>
-  <si>
-    <t>8016474</t>
-  </si>
-  <si>
-    <t>Área de Transparencia</t>
-  </si>
-  <si>
-    <t>A984CE1C6A57C05A67AB036922DCBFA6</t>
-  </si>
-  <si>
-    <t>01/04/2023</t>
-  </si>
-  <si>
-    <t>30/06/2023</t>
-  </si>
-  <si>
-    <t>8016517</t>
-  </si>
-  <si>
-    <t>12/07/2023</t>
-  </si>
-  <si>
-    <t>Privada</t>
-  </si>
-  <si>
-    <t>Eje vial</t>
-  </si>
-  <si>
-    <t>Circunvalación</t>
-  </si>
-  <si>
-    <t>Brecha</t>
-  </si>
-  <si>
-    <t>Diagonal</t>
-  </si>
-  <si>
-    <t>Calle</t>
-  </si>
-  <si>
-    <t>Corredor</t>
-  </si>
-  <si>
-    <t>Circuito</t>
-  </si>
-  <si>
-    <t>Pasaje</t>
-  </si>
-  <si>
-    <t>Vereda</t>
-  </si>
-  <si>
-    <t>Calzada</t>
-  </si>
-  <si>
-    <t>Viaducto</t>
-  </si>
-  <si>
-    <t>Prolongación</t>
-  </si>
-  <si>
-    <t>Boulevard</t>
-  </si>
-  <si>
-    <t>Peatonal</t>
-  </si>
-  <si>
-    <t>Retorno</t>
-  </si>
-  <si>
-    <t>Camino</t>
-  </si>
-  <si>
-    <t>Callejón</t>
-  </si>
-  <si>
-    <t>Cerrada</t>
-  </si>
-  <si>
-    <t>Ampliación</t>
-  </si>
-  <si>
-    <t>Continuación</t>
-  </si>
-  <si>
-    <t>Terracería</t>
-  </si>
-  <si>
-    <t>Andador</t>
-  </si>
-  <si>
-    <t>Periférico</t>
-  </si>
-  <si>
-    <t>Avenida</t>
-  </si>
-  <si>
-    <t>Aeropuerto</t>
-  </si>
-  <si>
-    <t>Barrio</t>
-  </si>
-  <si>
-    <t>Cantón</t>
-  </si>
-  <si>
-    <t>Ciudad industrial</t>
-  </si>
-  <si>
-    <t>Colonia</t>
-  </si>
-  <si>
-    <t>Condominio</t>
-  </si>
-  <si>
-    <t>Conjunto habitacional</t>
-  </si>
-  <si>
-    <t>Corredor industrial</t>
-  </si>
-  <si>
-    <t>Coto</t>
-  </si>
-  <si>
-    <t>Cuartel</t>
-  </si>
-  <si>
-    <t>Ejido</t>
-  </si>
-  <si>
-    <t>Exhacienda</t>
-  </si>
-  <si>
-    <t>Fracción</t>
-  </si>
-  <si>
-    <t>Fraccionamiento</t>
-  </si>
-  <si>
-    <t>Granja</t>
-  </si>
-  <si>
-    <t>Hacienda</t>
-  </si>
-  <si>
-    <t>Ingenio</t>
-  </si>
-  <si>
-    <t>Manzana</t>
-  </si>
-  <si>
-    <t>Paraje</t>
-  </si>
-  <si>
-    <t>Parque industrial</t>
-  </si>
-  <si>
-    <t>Pueblo</t>
-  </si>
-  <si>
-    <t>Puerto</t>
-  </si>
-  <si>
-    <t>Ranchería</t>
-  </si>
-  <si>
-    <t>Rancho</t>
-  </si>
-  <si>
-    <t>Región</t>
-  </si>
-  <si>
-    <t>Residencial</t>
-  </si>
-  <si>
-    <t>Rinconada</t>
-  </si>
-  <si>
-    <t>Sección</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Supermanzana</t>
-  </si>
-  <si>
-    <t>Unidad</t>
-  </si>
-  <si>
-    <t>Unidad habitacional</t>
-  </si>
-  <si>
-    <t>Villa</t>
-  </si>
-  <si>
-    <t>Zona federal</t>
-  </si>
-  <si>
-    <t>Zona industrial</t>
-  </si>
-  <si>
-    <t>Zona militar</t>
-  </si>
-  <si>
-    <t>Zona naval</t>
-  </si>
-  <si>
-    <t>Guerrero</t>
-  </si>
-  <si>
-    <t>Puebla</t>
-  </si>
-  <si>
-    <t>Quintana Roo</t>
-  </si>
-  <si>
-    <t>Guanajuato</t>
-  </si>
-  <si>
-    <t>Durango</t>
-  </si>
-  <si>
-    <t>Michoacán de Ocampo</t>
-  </si>
-  <si>
-    <t>San Luis Potosí</t>
-  </si>
-  <si>
-    <t>Campeche</t>
-  </si>
-  <si>
-    <t>Coahuila de Zaragoza</t>
-  </si>
-  <si>
-    <t>Nayarit</t>
-  </si>
-  <si>
-    <t>Zacatecas</t>
-  </si>
-  <si>
-    <t>Morelos</t>
-  </si>
-  <si>
-    <t>Sonora</t>
-  </si>
-  <si>
-    <t>Baja California Sur</t>
-  </si>
-  <si>
-    <t>Colima</t>
-  </si>
-  <si>
-    <t>Tabasco</t>
-  </si>
-  <si>
-    <t>Oaxaca</t>
-  </si>
-  <si>
-    <t>Jalisco</t>
-  </si>
-  <si>
-    <t>Chiapas</t>
-  </si>
-  <si>
-    <t>Hidalgo</t>
-  </si>
-  <si>
-    <t>Aguascalientes</t>
-  </si>
-  <si>
-    <t>Tamaulipas</t>
-  </si>
-  <si>
-    <t>Sinaloa</t>
-  </si>
-  <si>
-    <t>Yucatán</t>
-  </si>
-  <si>
-    <t>Chihuahua</t>
-  </si>
-  <si>
-    <t>Querétaro</t>
-  </si>
-  <si>
-    <t>Nuevo León</t>
-  </si>
-  <si>
-    <t>Veracruz de Ignacio de la Llave</t>
-  </si>
-  <si>
-    <t>Ciudad de México</t>
-  </si>
-  <si>
-    <t>Baja California</t>
-  </si>
-  <si>
-    <t>56316</t>
-  </si>
-  <si>
-    <t>56317</t>
-  </si>
-  <si>
-    <t>56318</t>
-  </si>
-  <si>
-    <t>77813</t>
-  </si>
-  <si>
-    <t>56319</t>
-  </si>
-  <si>
-    <t>56320</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Nombre(s)</t>
-  </si>
-  <si>
-    <t>Primer apellido</t>
-  </si>
-  <si>
-    <t>Segundo apellido</t>
-  </si>
-  <si>
-    <t>Sexo (catálogo)</t>
-  </si>
-  <si>
-    <t>Cargo o puesto en el sujeto obligado</t>
-  </si>
-  <si>
-    <t>Cargo o función en la UT</t>
-  </si>
-  <si>
-    <t>EF575B64D65263B8C79BD91735AD5241</t>
+    <t>15F187DD5DCC75649702D9F432DA24AD</t>
+  </si>
+  <si>
+    <t>Martín</t>
+  </si>
+  <si>
+    <t>Gonzalez</t>
+  </si>
+  <si>
+    <t>Hernandez</t>
+  </si>
+  <si>
+    <t>Tecnico Especializado B</t>
+  </si>
+  <si>
+    <t>15F187DD5DCC756432B19D521273EC5D</t>
   </si>
   <si>
     <t>Octavio</t>
@@ -640,46 +691,28 @@
     <t>Carbajal</t>
   </si>
   <si>
-    <t>Hernandez</t>
-  </si>
-  <si>
-    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
-  </si>
-  <si>
-    <t>Secretario de dirección de Plantel</t>
-  </si>
-  <si>
-    <t>Personal habilitado, para dar cumplimiento a las obligaciones de transparencia</t>
-  </si>
-  <si>
-    <t>EF575B64D65263B877D2C04AE1C1836F</t>
-  </si>
-  <si>
-    <t>Martín</t>
-  </si>
-  <si>
-    <t>Gonzalez</t>
-  </si>
-  <si>
-    <t>Técnico especializado B</t>
-  </si>
-  <si>
-    <t>EF575B64D65263B8E10992AF04AF28FE</t>
-  </si>
-  <si>
-    <t>Francisco Rene</t>
-  </si>
-  <si>
-    <t>Zempoalteca</t>
-  </si>
-  <si>
-    <t>Sanchez</t>
-  </si>
-  <si>
-    <t>Capturista</t>
-  </si>
-  <si>
-    <t>Hombre</t>
+    <t>Secretario de Dirección de Plantel</t>
+  </si>
+  <si>
+    <t>C8308AFFF0C087D88AC462177DF3A344</t>
+  </si>
+  <si>
+    <t>C8308AFFF0C087D89B10FC936B04D5E0</t>
+  </si>
+  <si>
+    <t>C8308AFFF0C087D8899F2C5F09BC3427</t>
+  </si>
+  <si>
+    <t>E5B5CC6D286D2E0FA45118B9D4D120F4</t>
+  </si>
+  <si>
+    <t>Eduardo Antonio</t>
+  </si>
+  <si>
+    <t>Betancour</t>
+  </si>
+  <si>
+    <t>Responsable del Area de Transparencia y Archivos</t>
   </si>
   <si>
     <t>Mujer</t>
@@ -688,7 +721,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -787,6 +820,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -802,44 +838,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -867,14 +903,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -902,6 +955,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -913,175 +983,151 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -1104,20 +1150,19 @@
     <col min="22" max="22" width="43.5703125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="31.5703125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="255" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="43" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="61.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="93.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="8" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1134,7 +1179,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -1149,7 +1194,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1229,16 +1274,13 @@
         <v>9</v>
       </c>
       <c r="AB4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -1323,13 +1365,10 @@
       <c r="AC5" t="s">
         <v>41</v>
       </c>
-      <c r="AD5" t="s">
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1359,192 +1398,185 @@
       <c r="AA6" s="5"/>
       <c r="AB6" s="5"/>
       <c r="AC6" s="5"/>
-      <c r="AD6" s="5"/>
-    </row>
-    <row r="7" spans="1:30" ht="26.25" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:29" ht="39" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="P7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="U7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="V7" s="2" t="s">
+      <c r="W7" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="X7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="Y7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="AA7" s="2" t="s">
+      <c r="AB7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AB7" s="2" t="s">
+      <c r="AC7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AC7" s="2" t="s">
+    </row>
+    <row r="8" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>78</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="S8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="V8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="W8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="V8" s="3" t="s">
+      <c r="X8" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="Y8" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="AC8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD8" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AD6"/>
+    <mergeCell ref="A6:AC6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1553,13 +1585,13 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I199" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>Hidden_28</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P8:P200">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P8:P199" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>Hidden_315</formula1>
     </dataValidation>
   </dataValidations>
@@ -1568,43 +1600,43 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -1708,7 +1740,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1734,7 +1766,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -1824,7 +1856,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -1923,13 +1955,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -2019,7 +2051,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
@@ -2093,21 +2125,22 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="181.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="67" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>6</v>
       </c>
@@ -2124,10 +2157,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>188</v>
       </c>
@@ -2146,142 +2182,243 @@
       <c r="H2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>214</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>95</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F4:F201" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>Hidden_1_Tabla_4359145</formula1>
     </dataValidation>
   </dataValidations>
@@ -2290,18 +2427,18 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIII/LTAIPT_A63F13.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2024/2DO_TRIMESTRE/FRACCIONES XI-XX/FRACC XIII/LTAIPT_A63F13.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\SEGUNDO TRIMESTRE ABRIL-JUNIO 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\COBAT\Downloads\TERCER TRIMESTRE JULIO-SEPTIEMBRE 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47656CA-97AC-492C-86CC-9ADCD639C9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC62CD3-C2FC-4D5C-8282-469DB97D3A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="230">
   <si>
     <t>48960</t>
   </si>
@@ -244,12 +244,18 @@
     <t>Nota</t>
   </si>
   <si>
+    <t>D61D7B918C75F731D01788F9B6ED2AFF</t>
+  </si>
+  <si>
     <t>2024</t>
   </si>
   <si>
     <t>01/07/2024</t>
   </si>
   <si>
+    <t>30/09/2024</t>
+  </si>
+  <si>
     <t>Carretera</t>
   </si>
   <si>
@@ -283,6 +289,9 @@
     <t>246-46-2-08-12</t>
   </si>
   <si>
+    <t>211</t>
+  </si>
+  <si>
     <t>08:30 a 17:30</t>
   </si>
   <si>
@@ -292,19 +301,16 @@
     <t>Se reciben solicitudes de información pública respecto al Colegio de Bachileres del Estado de Tlaxcala, a través del correo electrónico oficial de la Unidad de Transparencia, en el domicilio oficial de ésta, vía telefónica, por correo postal, mensajería, telégrafo, verbalmente ante el personal habilitado que las capturará en el sistema electrónico de solicitudes; o cualquier medio aprobado por el Sistema Nacional</t>
   </si>
   <si>
+    <t>https://buscador.plataformadetransparencia.org.mx/</t>
+  </si>
+  <si>
     <t>15984583</t>
   </si>
   <si>
-    <t>F99A931FA6631C9E56FB9265241B927D</t>
-  </si>
-  <si>
-    <t>01/04/2024</t>
-  </si>
-  <si>
-    <t>30/06/2024</t>
-  </si>
-  <si>
-    <t>http://www.infomextlaxcala.org.mx/</t>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>10/10/2024</t>
   </si>
   <si>
     <t>14416153</t>
@@ -1487,91 +1493,91 @@
     </row>
     <row r="8" spans="1:29" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="U8" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Y8" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z8" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="Z8" s="3" t="s">
+      <c r="AA8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AA8" s="3" t="s">
+      <c r="AB8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="AC8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1606,132 +1612,132 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -1746,207 +1752,207 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1961,162 +1967,162 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2165,255 +2171,255 @@
     </row>
     <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2433,12 +2439,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
